--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נטע ברזילי – גם זה יגיע</v>
+        <v>רון דבני – מה אני אגיד לך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%98%d7%a2-%d7%91%d7%a8%d7%96%d7%99%d7%9c%d7%99-%d7%92%d7%9d-%d7%96%d7%94-%d7%99%d7%92%d7%99%d7%a2/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%9f-%d7%93%d7%91%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%90%d7%92%d7%99%d7%93-%d7%9c%d7%9a/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-15</v>
+        <v>2026-03-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>את נטע ברזילי מעולם לא שמענו כל כך נרגשת וכאובה. “גם זה יגיע” הוא שיר החמצה שנשען על פרדוקס כואב מאוד: יש רצון לאהוב, יש אפילו הבטחה לאהוב, אבל אין יכולת ממשית לממש את האהבה בהווה. זה מה שהופך אותו</v>
+        <v>רון דבני שר שיר מחאה חד, חכם ומטריד, שפועל במסווה של שיר קצבי כמעט קליל, אבל בתוכו יושב טקסט אפל מאוד על כוח, הדחקה, חרדה מחשיפה, והתפוררות של מנגנוני הגנה גבריים. זה בדיוק אחד הכוחות שלו: המוזיקה עולה על “נתיב</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נטע ברזילי – גם זה יגיע</v>
+        <v>רון דבני – מה אני אגיד לך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רון דבני – מה אני אגיד לך</v>
+        <v>יהורם גאון – עד עולם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%9f-%d7%93%d7%91%d7%a0%d7%99-%d7%9e%d7%94-%d7%90%d7%a0%d7%99-%d7%90%d7%92%d7%99%d7%93-%d7%9c%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%a2%d7%93-%d7%a2%d7%95%d7%9c%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-16</v>
+        <v>2026-03-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>רון דבני שר שיר מחאה חד, חכם ומטריד, שפועל במסווה של שיר קצבי כמעט קליל, אבל בתוכו יושב טקסט אפל מאוד על כוח, הדחקה, חרדה מחשיפה, והתפוררות של מנגנוני הגנה גבריים. זה בדיוק אחד הכוחות שלו: המוזיקה עולה על “נתיב</v>
+        <v>השיר ששר יהורם גאון יושב על התפר שבין נוסטלגיה ישראלית קלאסית לבין עדכון עכשווי – וזה מורגש גם ברמת המילים וגם ברמת ההקשר. על פניו זה שיר אהבה בין גבר לאישה – “שלך הנני”, “את לעד תהיי לי”. אבל יש</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רון דבני – מה אני אגיד לך</v>
+        <v>יהורם גאון – עד עולם</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהורם גאון – עד עולם</v>
+        <v>מכלוף – תשמור עליי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%a2%d7%93-%d7%a2%d7%95%d7%9c%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%9b%d7%9c%d7%95%d7%a3-%d7%aa%d7%a9%d7%9e%d7%95%d7%a8-%d7%a2%d7%9c%d7%99%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-17</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר ששר יהורם גאון יושב על התפר שבין נוסטלגיה ישראלית קלאסית לבין עדכון עכשווי – וזה מורגש גם ברמת המילים וגם ברמת ההקשר. על פניו זה שיר אהבה בין גבר לאישה – “שלך הנני”, “את לעד תהיי לי”. אבל יש</v>
+        <v>הקאבר של “תשמור עליי” של מכלוף לשיר “תשמור על העולם ילד” של דוד ד'אור הוא לא רק ביצוע מחדש – אלא פרשנות רגשית ועדכנית שמזיזה את מרכז הכובד של השיר. הגרסה החדשה היא פחות תמימה, יותר חשופה, ופונה פנימה במקום</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהורם גאון – עד עולם</v>
+        <v>מכלוף – תשמור עליי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מכלוף – תשמור עליי</v>
+        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%9b%d7%9c%d7%95%d7%a3-%d7%aa%d7%a9%d7%9e%d7%95%d7%a8-%d7%a2%d7%9c%d7%99%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%91%d7%95%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-17</v>
+        <v>2026-03-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר של “תשמור עליי” של מכלוף לשיר “תשמור על העולם ילד” של דוד ד'אור הוא לא רק ביצוע מחדש – אלא פרשנות רגשית ועדכנית שמזיזה את מרכז הכובד של השיר. הגרסה החדשה היא פחות תמימה, יותר חשופה, ופונה פנימה במקום</v>
+        <v>השיר הוא דוגמה מדויקת למה שעילי בוטנר עושה כבר שנים – אבל כאן, בתוך תקופה טעונה וקשה, הןא מקבל משמעות אחרת: פחות “שיר נעים”, יותר שיר הישרדות רגשי. זה שיר שמכוון להיות פשוט – אבל מתחת לפשטות יש כמיהה עמוקה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מכלוף – תשמור עליי</v>
+        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
+        <v>תמר כהנא – לנצנץ</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%99%d7%9c%d7%99-%d7%91%d7%95%d7%98%d7%a0%d7%a8-%d7%95%d7%94%d7%99%d7%9c%d7%93%d7%99%d7%9d-%d7%94%d7%97%d7%93%d7%a9%d7%99%d7%9d-%d7%91%d7%95%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%9b%d7%94%d7%a0%d7%90-%d7%9c%d7%a0%d7%a6%d7%a0%d7%a5/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-18</v>
+        <v>2026-03-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר הוא דוגמה מדויקת למה שעילי בוטנר עושה כבר שנים – אבל כאן, בתוך תקופה טעונה וקשה, הןא מקבל משמעות אחרת: פחות “שיר נעים”, יותר שיר הישרדות רגשי. זה שיר שמכוון להיות פשוט – אבל מתחת לפשטות יש כמיהה עמוקה</v>
+        <v>השיר “לנצנץ” של תמר כהנא מתבססת פחות על “מבנה פופ” ויותר על תודעה מתפרקת בזמן אמת. זה לא שיר שמנסה להיות יפה – אלא כזה שחותר להיות אמיתי, חשוף מאוד –  גם אם זה לא נוח. זה שיר על קשר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עילי בוטנר והילדים החדשים – בוא לאור</v>
+        <v>תמר כהנא – לנצנץ</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר כהנא – לנצנץ</v>
+        <v>אייל גולן – בית מזכוכית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%9b%d7%94%d7%a0%d7%90-%d7%9c%d7%a0%d7%a6%d7%a0%d7%a5/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%92%d7%95%d7%9c%d7%9f-%d7%91%d7%99%d7%aa-%d7%9e%d7%96%d7%9b%d7%95%d7%9b%d7%99%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-19</v>
+        <v>2026-03-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “לנצנץ” של תמר כהנא מתבססת פחות על “מבנה פופ” ויותר על תודעה מתפרקת בזמן אמת. זה לא שיר שמנסה להיות יפה – אלא כזה שחותר להיות אמיתי, חשוף מאוד –  גם אם זה לא נוח. זה שיר על קשר</v>
+        <v>מצד אחד השיר “בית מזכוכית” של אייל גולן הוא  בלדת רגש קלאסית, עשויה היטב. מצד שני – טקסט שמבקש אמפתיה ציבורית מדמות ציבורית שנויה במחלוקת. זה שיר שמנסה להפוך ביקורת ציבורית לכאב אישי – בהצלחה מוזיקלית, אבל עם מורכבות רעיונית</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר כהנא – לנצנץ</v>
+        <v>אייל גולן – בית מזכוכית</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן – בית מזכוכית</v>
+        <v>זיו כהן – ימי הביניים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-21</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%92%d7%95%d7%9c%d7%9f-%d7%91%d7%99%d7%aa-%d7%9e%d7%96%d7%9b%d7%95%d7%9b%d7%99%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%96%d7%99%d7%95-%d7%9b%d7%94%d7%9f-%d7%99%d7%9e%d7%99-%d7%94%d7%91%d7%99%d7%a0%d7%99%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-21</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מצד אחד השיר “בית מזכוכית” של אייל גולן הוא  בלדת רגש קלאסית, עשויה היטב. מצד שני – טקסט שמבקש אמפתיה ציבורית מדמות ציבורית שנויה במחלוקת. זה שיר שמנסה להפוך ביקורת ציבורית לכאב אישי – בהצלחה מוזיקלית, אבל עם מורכבות רעיונית</v>
+        <v>השיר “ימי הביניים” של זיו כהן מנסה לעשות מהלך שאפתני: לקחת ראפ אישי ועכשווי – ולהלביש עליו עולם דימויים היסטורי־אפי. התוצאה היא שיר שמתקיים בין שני צירים: פנימי (נפשי) ו־חיצוני (מיתולוגי/היסטורי). זה שיר שמצליח לייצר אווירה חזקה וזהות סאונדית ייחודית,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן – בית מזכוכית</v>
+        <v>זיו כהן – ימי הביניים</v>
       </c>
     </row>
   </sheetData>
